--- a/tests/output_excel_multi.xlsx
+++ b/tests/output_excel_multi.xlsx
@@ -7,8 +7,8 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Gastos" sheetId="1" r:id="rId1"/>
-    <sheet name="Ventas" sheetId="2" r:id="rId2"/>
+    <sheet name="Ventas" sheetId="1" r:id="rId1"/>
+    <sheet name="Gastos" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17,6 +17,18 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>total</t>
+  </si>
+  <si>
+    <t>Norte</t>
+  </si>
+  <si>
+    <t>Sur</t>
+  </si>
+  <si>
     <t>concepto</t>
   </si>
   <si>
@@ -30,18 +42,6 @@
   </si>
   <si>
     <t>Servicios</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>total</t>
-  </si>
-  <si>
-    <t>Norte</t>
-  </si>
-  <si>
-    <t>Sur</t>
   </si>
 </sst>
 </file>
@@ -388,20 +388,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>30000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>2000</v>
@@ -409,7 +443,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>15000</v>
@@ -417,44 +451,10 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>800</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>30000</v>
       </c>
     </row>
   </sheetData>
